--- a/data/2026-10-05/榜单.xlsx
+++ b/data/2026-10-05/榜单.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Top20" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全部候选" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="升温领域" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -64,7 +65,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -79,6 +80,7 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -7413,4 +7415,355 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="48" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>话题</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>今日条数</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>今日均分</t>
+        </is>
+      </c>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>今日最高分</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
+          <t>近7天均值条数</t>
+        </is>
+      </c>
+      <c r="F1" s="6" t="inlineStr">
+        <is>
+          <t>判定依据</t>
+        </is>
+      </c>
+      <c r="G1" s="6" t="inlineStr">
+        <is>
+          <t>代表内容</t>
+        </is>
+      </c>
+      <c r="H1" s="6" t="inlineStr">
+        <is>
+          <t>链接</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Anthropic/Claude</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>55.9</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>首次出现当天即进Top10</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>🚨 REVERSE ENGINEER ANY APP, THEN HAND IT TO YOUR AGENT
+REA is an open-source toolkit that plugs reverse engineering int</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@whitewhoadie/video/7692856072624770318</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>首次出现当天即进Top10</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>I quit OpenAI because its culture is broken</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>https://www.theatlantic.com/technology/2026/10/openai-safety-team-resignation/688881/?gift=v5U_UzUTothfWXsPxtvNVAh7esWToMRD6XnbXmc5WgA</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>AI编程</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>首次出现当天即进Top10</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Getting the most out of Opus 5.5 in Claude and Claude Code</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>https://claude.dev/blog/getting-the-most-out-of-opus-5-5/</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>AI Agent</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>首次出现当天即进Top10</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>🚨 REVERSE ENGINEER ANY APP, THEN HAND IT TO YOUR AGENT
+REA is an open-source toolkit that plugs reverse engineering int</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@whitewhoadie/video/7692856072624770318</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Google/Gemini</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>首次出现当天即进Top10</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>🚨 REVERSE ENGINEER ANY APP, THEN HAND IT TO YOUR AGENT
+REA is an open-source toolkit that plugs reverse engineering int</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@whitewhoadie/video/7692856072624770318</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>AI视频生成</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>79.40000000000001</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>首次出现当天即进Top10</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>Wait until the end 🤯 LTX 2.5 AI Video Generator is changing AI video generation with cinematic text-to-video! #LTX25 #LT</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@benkimball.ai/video/7692264115812732190</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>开源模型</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>88.2</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>首次出现当天即进Top10</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Aleph Alpha Kolibri: How the sovereign German LLM works</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>https://tej.as/blog/aleph-alpha-kolibri</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Qwen/阿里</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>首次出现当天即进Top10</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>Run Qwen 3.8 Flash Next (125B) on consumer hardware (RTX 4090) at 100T/s</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/Niko1221/Strata</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId8"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>